--- a/docs/Sundial_Customer__c_Field_Design.xlsx
+++ b/docs/Sundial_Customer__c_Field_Design.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TimMurphy\Projects\harmon-crm\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TimMurphy\Projects\sundial-core\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E72BD56-D313-4F4D-A12F-92E64684358A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D67B20E9-2A27-471E-9312-69882B1E7B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fields by Section" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2648" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="852">
   <si>
     <t>Sundial Section</t>
   </si>
@@ -2531,6 +2531,51 @@
   </si>
   <si>
     <t>hidden</t>
+  </si>
+  <si>
+    <t>NS Adder 1 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_1_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price of NS Adder 1</t>
+  </si>
+  <si>
+    <t>NS Adder 2 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_2_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price of NS Adder 2</t>
+  </si>
+  <si>
+    <t>NS Adder 3 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_3_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price of NS Adder 3</t>
+  </si>
+  <si>
+    <t>NS Adder 4 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_4_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price of NS Adder 4</t>
+  </si>
+  <si>
+    <t>NS Adder 5 Price</t>
+  </si>
+  <si>
+    <t>NS_Adder_5_Price__c</t>
+  </si>
+  <si>
+    <t>Computed price of NS Adder 5</t>
   </si>
 </sst>
 </file>
@@ -2907,7 +2952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H331"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.875" customWidth="1"/>
@@ -10563,19 +10608,13 @@
         <v>597</v>
       </c>
       <c r="B295" t="s">
-        <v>738</v>
+        <v>837</v>
       </c>
       <c r="C295" t="s">
-        <v>739</v>
-      </c>
-      <c r="D295" t="s">
-        <v>726</v>
+        <v>838</v>
       </c>
       <c r="E295" t="s">
-        <v>727</v>
-      </c>
-      <c r="F295" t="s">
-        <v>11</v>
+        <v>839</v>
       </c>
       <c r="G295" t="s">
         <v>835</v>
@@ -10589,25 +10628,25 @@
         <v>597</v>
       </c>
       <c r="B296" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C296" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D296" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E296" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F296" t="s">
         <v>11</v>
       </c>
       <c r="G296" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H296" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
@@ -10615,16 +10654,16 @@
         <v>597</v>
       </c>
       <c r="B297" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C297" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D297" t="s">
-        <v>510</v>
+        <v>730</v>
       </c>
       <c r="E297" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="F297" t="s">
         <v>11</v>
@@ -10641,16 +10680,16 @@
         <v>597</v>
       </c>
       <c r="B298" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C298" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D298" t="s">
-        <v>586</v>
+        <v>510</v>
       </c>
       <c r="E298" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="F298" t="s">
         <v>11</v>
@@ -10667,25 +10706,25 @@
         <v>597</v>
       </c>
       <c r="B299" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C299" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D299" t="s">
-        <v>726</v>
+        <v>586</v>
       </c>
       <c r="E299" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="F299" t="s">
         <v>11</v>
       </c>
       <c r="G299" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H299" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
@@ -10693,25 +10732,19 @@
         <v>597</v>
       </c>
       <c r="B300" t="s">
-        <v>748</v>
+        <v>840</v>
       </c>
       <c r="C300" t="s">
-        <v>749</v>
-      </c>
-      <c r="D300" t="s">
-        <v>730</v>
+        <v>841</v>
       </c>
       <c r="E300" t="s">
-        <v>731</v>
-      </c>
-      <c r="F300" t="s">
-        <v>11</v>
+        <v>842</v>
       </c>
       <c r="G300" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H300" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
@@ -10719,25 +10752,25 @@
         <v>597</v>
       </c>
       <c r="B301" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C301" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="D301" t="s">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="E301" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="F301" t="s">
         <v>11</v>
       </c>
       <c r="G301" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H301" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
@@ -10745,16 +10778,16 @@
         <v>597</v>
       </c>
       <c r="B302" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C302" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="D302" t="s">
-        <v>586</v>
+        <v>730</v>
       </c>
       <c r="E302" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="F302" t="s">
         <v>11</v>
@@ -10771,25 +10804,25 @@
         <v>597</v>
       </c>
       <c r="B303" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="C303" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="D303" t="s">
-        <v>726</v>
+        <v>510</v>
       </c>
       <c r="E303" t="s">
-        <v>11</v>
+        <v>734</v>
       </c>
       <c r="F303" t="s">
         <v>11</v>
       </c>
       <c r="G303" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H303" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
@@ -10797,16 +10830,16 @@
         <v>597</v>
       </c>
       <c r="B304" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="C304" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="D304" t="s">
-        <v>730</v>
+        <v>586</v>
       </c>
       <c r="E304" t="s">
-        <v>11</v>
+        <v>737</v>
       </c>
       <c r="F304" t="s">
         <v>11</v>
@@ -10823,25 +10856,19 @@
         <v>597</v>
       </c>
       <c r="B305" t="s">
-        <v>758</v>
+        <v>843</v>
       </c>
       <c r="C305" t="s">
-        <v>759</v>
-      </c>
-      <c r="D305" t="s">
-        <v>510</v>
+        <v>844</v>
       </c>
       <c r="E305" t="s">
-        <v>11</v>
-      </c>
-      <c r="F305" t="s">
-        <v>11</v>
+        <v>845</v>
       </c>
       <c r="G305" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H305" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
@@ -10849,13 +10876,13 @@
         <v>597</v>
       </c>
       <c r="B306" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="C306" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="D306" t="s">
-        <v>586</v>
+        <v>726</v>
       </c>
       <c r="E306" t="s">
         <v>11</v>
@@ -10864,10 +10891,10 @@
         <v>11</v>
       </c>
       <c r="G306" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H306" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
@@ -10875,13 +10902,13 @@
         <v>597</v>
       </c>
       <c r="B307" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="C307" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="D307" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E307" t="s">
         <v>11</v>
@@ -10890,10 +10917,10 @@
         <v>11</v>
       </c>
       <c r="G307" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H307" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
@@ -10901,13 +10928,13 @@
         <v>597</v>
       </c>
       <c r="B308" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C308" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="D308" t="s">
-        <v>730</v>
+        <v>510</v>
       </c>
       <c r="E308" t="s">
         <v>11</v>
@@ -10927,13 +10954,13 @@
         <v>597</v>
       </c>
       <c r="B309" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C309" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="D309" t="s">
-        <v>510</v>
+        <v>586</v>
       </c>
       <c r="E309" t="s">
         <v>11</v>
@@ -10953,68 +10980,62 @@
         <v>597</v>
       </c>
       <c r="B310" t="s">
-        <v>768</v>
+        <v>846</v>
       </c>
       <c r="C310" t="s">
-        <v>769</v>
-      </c>
-      <c r="D310" t="s">
-        <v>586</v>
+        <v>847</v>
       </c>
       <c r="E310" t="s">
-        <v>11</v>
-      </c>
-      <c r="F310" t="s">
-        <v>11</v>
+        <v>848</v>
       </c>
       <c r="G310" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H310" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>770</v>
+        <v>597</v>
       </c>
       <c r="B311" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="C311" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="D311" t="s">
-        <v>773</v>
+        <v>726</v>
       </c>
       <c r="E311" t="s">
-        <v>774</v>
+        <v>11</v>
       </c>
       <c r="F311" t="s">
         <v>11</v>
       </c>
       <c r="G311" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H311" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>770</v>
+        <v>597</v>
       </c>
       <c r="B312" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="C312" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="D312" t="s">
-        <v>773</v>
+        <v>730</v>
       </c>
       <c r="E312" t="s">
-        <v>777</v>
+        <v>11</v>
       </c>
       <c r="F312" t="s">
         <v>11</v>
@@ -11028,19 +11049,19 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>770</v>
+        <v>597</v>
       </c>
       <c r="B313" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="C313" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="D313" t="s">
         <v>510</v>
       </c>
       <c r="E313" t="s">
-        <v>780</v>
+        <v>11</v>
       </c>
       <c r="F313" t="s">
         <v>11</v>
@@ -11054,19 +11075,19 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>770</v>
+        <v>597</v>
       </c>
       <c r="B314" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="C314" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="D314" t="s">
-        <v>563</v>
+        <v>586</v>
       </c>
       <c r="E314" t="s">
-        <v>783</v>
+        <v>11</v>
       </c>
       <c r="F314" t="s">
         <v>11</v>
@@ -11080,25 +11101,19 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>770</v>
+        <v>597</v>
       </c>
       <c r="B315" t="s">
-        <v>784</v>
+        <v>849</v>
       </c>
       <c r="C315" t="s">
-        <v>785</v>
-      </c>
-      <c r="D315" t="s">
-        <v>411</v>
+        <v>850</v>
       </c>
       <c r="E315" t="s">
-        <v>786</v>
-      </c>
-      <c r="F315" t="s">
-        <v>11</v>
+        <v>851</v>
       </c>
       <c r="G315" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H315" t="s">
         <v>835</v>
@@ -11109,25 +11124,25 @@
         <v>770</v>
       </c>
       <c r="B316" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="C316" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="D316" t="s">
-        <v>411</v>
+        <v>773</v>
       </c>
       <c r="E316" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="F316" t="s">
         <v>11</v>
       </c>
       <c r="G316" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H316" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
@@ -11135,16 +11150,16 @@
         <v>770</v>
       </c>
       <c r="B317" t="s">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="C317" t="s">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="D317" t="s">
-        <v>411</v>
+        <v>773</v>
       </c>
       <c r="E317" t="s">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="F317" t="s">
         <v>11</v>
@@ -11153,7 +11168,7 @@
         <v>836</v>
       </c>
       <c r="H317" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
@@ -11161,16 +11176,16 @@
         <v>770</v>
       </c>
       <c r="B318" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="C318" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="D318" t="s">
-        <v>411</v>
+        <v>510</v>
       </c>
       <c r="E318" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="F318" t="s">
         <v>11</v>
@@ -11179,24 +11194,24 @@
         <v>836</v>
       </c>
       <c r="H318" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>796</v>
+        <v>770</v>
       </c>
       <c r="B319" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="C319" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="D319" t="s">
-        <v>799</v>
+        <v>563</v>
       </c>
       <c r="E319" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="F319" t="s">
         <v>11</v>
@@ -11210,19 +11225,19 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>796</v>
+        <v>770</v>
       </c>
       <c r="B320" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="C320" t="s">
-        <v>802</v>
+        <v>785</v>
       </c>
       <c r="D320" t="s">
-        <v>803</v>
+        <v>411</v>
       </c>
       <c r="E320" t="s">
-        <v>804</v>
+        <v>786</v>
       </c>
       <c r="F320" t="s">
         <v>11</v>
@@ -11231,50 +11246,50 @@
         <v>836</v>
       </c>
       <c r="H320" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>796</v>
+        <v>770</v>
       </c>
       <c r="B321" t="s">
-        <v>805</v>
+        <v>787</v>
       </c>
       <c r="C321" t="s">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="D321" t="s">
-        <v>807</v>
+        <v>411</v>
       </c>
       <c r="E321" t="s">
-        <v>804</v>
+        <v>789</v>
       </c>
       <c r="F321" t="s">
         <v>11</v>
       </c>
       <c r="G321" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H321" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>796</v>
+        <v>770</v>
       </c>
       <c r="B322" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="C322" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
       <c r="D322" t="s">
-        <v>166</v>
+        <v>411</v>
       </c>
       <c r="E322" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="F322" t="s">
         <v>11</v>
@@ -11283,24 +11298,24 @@
         <v>836</v>
       </c>
       <c r="H322" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>796</v>
+        <v>770</v>
       </c>
       <c r="B323" t="s">
-        <v>810</v>
+        <v>793</v>
       </c>
       <c r="C323" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
       <c r="D323" t="s">
-        <v>268</v>
+        <v>411</v>
       </c>
       <c r="E323" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="F323" t="s">
         <v>11</v>
@@ -11309,7 +11324,7 @@
         <v>836</v>
       </c>
       <c r="H323" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
@@ -11317,16 +11332,16 @@
         <v>796</v>
       </c>
       <c r="B324" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="C324" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="D324" t="s">
-        <v>166</v>
+        <v>799</v>
       </c>
       <c r="E324" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="F324" t="s">
         <v>11</v>
@@ -11343,13 +11358,13 @@
         <v>796</v>
       </c>
       <c r="B325" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="C325" t="s">
-        <v>815</v>
+        <v>802</v>
       </c>
       <c r="D325" t="s">
-        <v>268</v>
+        <v>803</v>
       </c>
       <c r="E325" t="s">
         <v>804</v>
@@ -11369,13 +11384,13 @@
         <v>796</v>
       </c>
       <c r="B326" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="C326" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="D326" t="s">
-        <v>268</v>
+        <v>807</v>
       </c>
       <c r="E326" t="s">
         <v>804</v>
@@ -11395,13 +11410,13 @@
         <v>796</v>
       </c>
       <c r="B327" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="C327" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="D327" t="s">
-        <v>36</v>
+        <v>166</v>
       </c>
       <c r="E327" t="s">
         <v>804</v>
@@ -11421,13 +11436,13 @@
         <v>796</v>
       </c>
       <c r="B328" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="C328" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="D328" t="s">
-        <v>43</v>
+        <v>268</v>
       </c>
       <c r="E328" t="s">
         <v>804</v>
@@ -11447,13 +11462,13 @@
         <v>796</v>
       </c>
       <c r="B329" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="C329" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="D329" t="s">
-        <v>268</v>
+        <v>166</v>
       </c>
       <c r="E329" t="s">
         <v>804</v>
@@ -11473,10 +11488,10 @@
         <v>796</v>
       </c>
       <c r="B330" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="C330" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="D330" t="s">
         <v>268</v>
@@ -11499,31 +11514,161 @@
         <v>796</v>
       </c>
       <c r="B331" t="s">
+        <v>816</v>
+      </c>
+      <c r="C331" t="s">
+        <v>817</v>
+      </c>
+      <c r="D331" t="s">
+        <v>268</v>
+      </c>
+      <c r="E331" t="s">
+        <v>804</v>
+      </c>
+      <c r="F331" t="s">
+        <v>11</v>
+      </c>
+      <c r="G331" t="s">
+        <v>836</v>
+      </c>
+      <c r="H331" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>796</v>
+      </c>
+      <c r="B332" t="s">
+        <v>818</v>
+      </c>
+      <c r="C332" t="s">
+        <v>819</v>
+      </c>
+      <c r="D332" t="s">
+        <v>36</v>
+      </c>
+      <c r="E332" t="s">
+        <v>804</v>
+      </c>
+      <c r="F332" t="s">
+        <v>11</v>
+      </c>
+      <c r="G332" t="s">
+        <v>836</v>
+      </c>
+      <c r="H332" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>796</v>
+      </c>
+      <c r="B333" t="s">
+        <v>820</v>
+      </c>
+      <c r="C333" t="s">
+        <v>821</v>
+      </c>
+      <c r="D333" t="s">
+        <v>43</v>
+      </c>
+      <c r="E333" t="s">
+        <v>804</v>
+      </c>
+      <c r="F333" t="s">
+        <v>11</v>
+      </c>
+      <c r="G333" t="s">
+        <v>836</v>
+      </c>
+      <c r="H333" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>796</v>
+      </c>
+      <c r="B334" t="s">
+        <v>822</v>
+      </c>
+      <c r="C334" t="s">
+        <v>823</v>
+      </c>
+      <c r="D334" t="s">
+        <v>268</v>
+      </c>
+      <c r="E334" t="s">
+        <v>804</v>
+      </c>
+      <c r="F334" t="s">
+        <v>11</v>
+      </c>
+      <c r="G334" t="s">
+        <v>836</v>
+      </c>
+      <c r="H334" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>796</v>
+      </c>
+      <c r="B335" t="s">
+        <v>824</v>
+      </c>
+      <c r="C335" t="s">
+        <v>825</v>
+      </c>
+      <c r="D335" t="s">
+        <v>268</v>
+      </c>
+      <c r="E335" t="s">
+        <v>804</v>
+      </c>
+      <c r="F335" t="s">
+        <v>11</v>
+      </c>
+      <c r="G335" t="s">
+        <v>836</v>
+      </c>
+      <c r="H335" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>796</v>
+      </c>
+      <c r="B336" t="s">
         <v>826</v>
       </c>
-      <c r="C331" t="s">
+      <c r="C336" t="s">
         <v>827</v>
       </c>
-      <c r="D331" t="s">
+      <c r="D336" t="s">
         <v>166</v>
       </c>
-      <c r="E331" t="s">
+      <c r="E336" t="s">
         <v>828</v>
       </c>
-      <c r="F331" t="s">
-        <v>11</v>
-      </c>
-      <c r="G331" t="s">
-        <v>836</v>
-      </c>
-      <c r="H331" t="s">
+      <c r="F336" t="s">
+        <v>11</v>
+      </c>
+      <c r="G336" t="s">
+        <v>836</v>
+      </c>
+      <c r="H336" t="s">
         <v>836</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A251:F331 A227:F227 A1:F137 A231:F246 A142:F224 B139:F139 B141:F141 A229:F230 A228:B228 E228:F228" numberStoredAsText="1"/>
+    <ignoredError sqref="A316:F336 A227:F227 A1:F137 A142:F224 B139:F139 B141:F141 A229:F246 A228:B228 E228:F228 A251:F294 A296:F299 A301:F304 A306:F309 A311:F314" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>